--- a/input/reg_socialcare.xlsx
+++ b/input/reg_socialcare.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="255">
   <si>
     <t>Description:</t>
   </si>
@@ -784,12 +784,18 @@
   <si>
     <t>S3d - Hours of informal care provided, Partnered</t>
   </si>
+  <si>
+    <t>healthPartnerSelfRatedExcellent</t>
+  </si>
+  <si>
+    <t>careMarketMixedPartner</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="410">
+  <fonts count="819">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2443,6 +2449,1670 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2453,7 +4123,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="396">
+  <borders count="791">
     <border>
       <left/>
       <right/>
@@ -5226,11 +6896,2776 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="396">
+  <cellXfs count="791">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -6809,6 +11244,1586 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="409" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="424" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="425" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="426" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="427" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="428" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="429" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="430" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="431" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="432" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="433" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="434" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="435" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="436" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="437" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="438" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="439" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="440" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="441" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="442" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="443" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="444" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="445" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="446" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="447" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="448" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="449" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="450" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="451" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="452" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="453" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="454" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="455" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="456" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="457" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="458" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="459" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="460" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="461" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="462" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="463" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="464" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="465" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="466" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="467" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="468" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="469" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="470" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="471" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="472" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="473" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="474" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="475" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="476" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="477" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="478" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="479" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="480" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="481" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="482" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="483" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="484" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="485" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="486" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="487" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="488" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="489" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="490" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="491" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="492" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="493" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="494" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="495" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="496" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="497" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="498" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="499" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="500" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="501" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="502" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="503" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="504" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="505" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="506" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="507" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="508" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="509" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="510" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="511" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="512" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="513" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="514" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="515" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="516" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="517" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="518" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="519" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="520" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="521" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="522" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="523" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="524" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="525" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="526" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="527" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="528" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="529" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="530" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="531" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="532" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="533" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="534" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="535" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="536" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="537" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="538" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="539" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="540" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="541" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="542" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="543" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="544" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="545" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="546" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="547" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="548" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="549" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="550" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="551" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="552" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="553" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="554" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="555" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="556" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="557" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="558" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="559" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="560" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="561" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="562" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="563" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="564" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="565" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="566" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="567" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="568" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="569" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="570" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="571" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="572" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="573" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="574" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="575" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="576" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="577" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="578" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="579" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="580" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="581" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="582" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="583" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="584" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="585" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="586" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="587" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="588" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="589" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="590" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="591" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="592" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="593" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="594" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="595" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="596" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="597" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="598" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="599" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="600" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="601" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="602" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="603" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="604" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="605" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="606" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="607" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="608" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="609" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="610" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="611" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="612" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="613" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="614" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="615" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="616" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="617" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="618" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="619" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="620" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="621" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="622" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="623" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="624" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="625" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="626" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="627" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="628" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="629" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="630" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="631" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="632" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="633" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="634" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="635" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="636" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="637" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="638" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="639" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="640" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="641" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="642" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="643" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="644" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="645" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="646" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="647" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="648" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="649" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="650" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="651" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="652" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="653" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="654" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="655" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="656" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="657" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="658" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="659" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="660" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="661" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="662" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="663" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="664" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="665" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="666" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="667" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="668" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="669" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="670" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="671" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="672" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="673" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="674" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="675" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="676" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="677" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="678" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="679" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="680" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="681" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="682" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="683" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="684" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="685" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="686" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="687" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="688" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="689" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="690" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="691" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="692" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="693" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="694" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="695" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="696" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="697" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="698" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="699" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="700" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="701" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="702" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="703" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="704" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="705" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="706" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="707" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="708" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="709" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="710" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="711" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="712" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="713" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="714" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="715" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="716" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="717" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="718" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="719" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="720" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="721" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="722" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="723" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="724" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="725" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="726" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="727" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="728" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="729" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="730" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="731" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="732" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="733" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="734" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="735" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="736" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="737" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="738" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="739" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="740" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="741" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="742" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="743" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="744" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="745" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="746" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="747" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="748" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="749" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="750" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="751" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="752" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="753" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="754" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="755" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="756" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="757" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="758" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="759" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="760" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="761" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="762" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="763" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="764" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="765" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="766" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="767" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="768" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="769" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="770" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="771" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="772" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="773" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="774" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="775" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="776" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="777" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="778" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="779" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="780" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="781" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="782" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="783" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="784" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="785" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="786" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="787" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="788" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="789" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="790" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="791" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="792" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="793" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="794" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="795" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="796" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="797" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="798" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="799" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="800" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="801" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="802" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="803" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="804" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="806" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="808" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="810" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="812" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="814" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="816" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="818" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6825,7 +12840,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="396" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -6849,10 +12864,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="397" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="398" t="s">
         <v>0</v>
       </c>
     </row>
@@ -6929,7 +12944,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="399" t="s">
         <v>25</v>
       </c>
       <c r="B20" t="s">
@@ -7000,7 +13015,7 @@
         <v>244</v>
       </c>
       <c r="Q1" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="R1" t="s">
         <v>236</v>
@@ -8782,7 +14797,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B16">
         <v>-0.85831712629375601</v>
@@ -18088,7 +24103,7 @@
         <v>240</v>
       </c>
       <c r="U1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="V1" t="s">
         <v>241</v>
@@ -18112,7 +24127,7 @@
         <v>244</v>
       </c>
       <c r="AC1" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="AD1" t="s">
         <v>236</v>
@@ -21030,7 +27045,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B20">
         <v>0.25276588368087149</v>
@@ -22294,7 +28309,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B28">
         <v>-0.64383071185575613</v>
@@ -26094,12 +32109,12 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="400" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="401" t="s">
         <v>67</v>
       </c>
     </row>
@@ -26132,7 +32147,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="402" t="s">
         <v>77</v>
       </c>
     </row>
@@ -26165,7 +32180,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="389" t="s">
+      <c r="A11" s="784" t="s">
         <v>213</v>
       </c>
     </row>
@@ -26198,7 +32213,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="390" t="s">
+      <c r="A15" s="785" t="s">
         <v>218</v>
       </c>
     </row>
@@ -26219,7 +32234,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="391" t="s">
+      <c r="A19" s="786" t="s">
         <v>221</v>
       </c>
     </row>
@@ -26240,7 +32255,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="392" t="s">
+      <c r="A23" s="787" t="s">
         <v>237</v>
       </c>
     </row>
@@ -26273,7 +32288,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="393" t="s">
+      <c r="A27" s="788" t="s">
         <v>246</v>
       </c>
     </row>
@@ -26306,7 +32321,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="394" t="s">
+      <c r="A31" s="789" t="s">
         <v>250</v>
       </c>
     </row>
@@ -26327,7 +32342,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="395" t="s">
+      <c r="A35" s="790" t="s">
         <v>252</v>
       </c>
     </row>
@@ -35915,1399 +41930,1399 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="403" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="404" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="405" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="406" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="407" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="408">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="409" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="410" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="411">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="412" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="413" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="414">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="415" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="416" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="417">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="418" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="419" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="420">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="421" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="422" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="423">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="424" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="425" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="426">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="427" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="428" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="429">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="430" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="431" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="432">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="433" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="434" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="435">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="436" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="437" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="438">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="439" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="440" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="46">
+      <c r="C13" s="441">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="442" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="443" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="49">
+      <c r="C14" s="444">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="445" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="446" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="52">
+      <c r="C15" s="447">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="448" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="449" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="55">
+      <c r="C16" s="450">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="451" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="452" t="s">
         <v>96</v>
       </c>
-      <c r="C17" s="58">
+      <c r="C17" s="453">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="454" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="60" t="s">
+      <c r="B18" s="455" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="61">
+      <c r="C18" s="456">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="457" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="B19" s="458" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="64">
+      <c r="C19" s="459">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="65" t="s">
+      <c r="A20" s="460" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="461" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="67">
+      <c r="C20" s="462">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="463" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="464" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="70">
+      <c r="C21" s="465">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="71" t="s">
+      <c r="A22" s="466" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="72" t="s">
+      <c r="B22" s="467" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="73">
+      <c r="C22" s="468">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="469" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="470" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="76">
+      <c r="C23" s="471">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="77" t="s">
+      <c r="A24" s="472" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="78" t="s">
+      <c r="B24" s="473" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="79">
+      <c r="C24" s="474">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="80" t="s">
+      <c r="A25" s="475" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="476" t="s">
         <v>104</v>
       </c>
-      <c r="C25" s="82">
+      <c r="C25" s="477">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="83" t="s">
+      <c r="A26" s="478" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="84" t="s">
+      <c r="B26" s="479" t="s">
         <v>105</v>
       </c>
-      <c r="C26" s="85">
+      <c r="C26" s="480">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="86" t="s">
+      <c r="A27" s="481" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="87" t="s">
+      <c r="B27" s="482" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="88">
+      <c r="C27" s="483">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="484" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="90" t="s">
+      <c r="B28" s="485" t="s">
         <v>107</v>
       </c>
-      <c r="C28" s="91">
+      <c r="C28" s="486">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="92" t="s">
+      <c r="A29" s="487" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="93" t="s">
+      <c r="B29" s="488" t="s">
         <v>108</v>
       </c>
-      <c r="C29" s="94">
+      <c r="C29" s="489">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="95" t="s">
+      <c r="A30" s="490" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="96" t="s">
+      <c r="B30" s="491" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="97">
+      <c r="C30" s="492">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="98" t="s">
+      <c r="A31" s="493" t="s">
         <v>78</v>
       </c>
-      <c r="B31" s="99" t="s">
+      <c r="B31" s="494" t="s">
         <v>110</v>
       </c>
-      <c r="C31" s="100">
+      <c r="C31" s="495">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="101" t="s">
+      <c r="A32" s="496" t="s">
         <v>78</v>
       </c>
-      <c r="B32" s="102" t="s">
+      <c r="B32" s="497" t="s">
         <v>111</v>
       </c>
-      <c r="C32" s="103">
+      <c r="C32" s="498">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="104" t="s">
+      <c r="A33" s="499" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="105" t="s">
+      <c r="B33" s="500" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="106">
+      <c r="C33" s="501">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="107" t="s">
+      <c r="A34" s="502" t="s">
         <v>78</v>
       </c>
-      <c r="B34" s="108" t="s">
+      <c r="B34" s="503" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="109">
+      <c r="C34" s="504">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="110" t="s">
+      <c r="A35" s="505" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="111" t="s">
+      <c r="B35" s="506" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="112">
+      <c r="C35" s="507">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="508" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="114" t="s">
+      <c r="B36" s="509" t="s">
         <v>115</v>
       </c>
-      <c r="C36" s="115">
+      <c r="C36" s="510">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="116" t="s">
+      <c r="A37" s="511" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="117" t="s">
+      <c r="B37" s="512" t="s">
         <v>116</v>
       </c>
-      <c r="C37" s="118">
+      <c r="C37" s="513">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="119" t="s">
+      <c r="A38" s="514" t="s">
         <v>78</v>
       </c>
-      <c r="B38" s="120" t="s">
+      <c r="B38" s="515" t="s">
         <v>117</v>
       </c>
-      <c r="C38" s="121">
+      <c r="C38" s="516">
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="122" t="s">
+      <c r="A39" s="517" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="123" t="s">
+      <c r="B39" s="518" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="124">
+      <c r="C39" s="519">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="125" t="s">
+      <c r="A40" s="520" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="126" t="s">
+      <c r="B40" s="521" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="127">
+      <c r="C40" s="522">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="128" t="s">
+      <c r="A41" s="523" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="129" t="s">
+      <c r="B41" s="524" t="s">
         <v>120</v>
       </c>
-      <c r="C41" s="130">
+      <c r="C41" s="525">
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="131" t="s">
+      <c r="A42" s="526" t="s">
         <v>78</v>
       </c>
-      <c r="B42" s="132" t="s">
+      <c r="B42" s="527" t="s">
         <v>121</v>
       </c>
-      <c r="C42" s="133">
+      <c r="C42" s="528">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="134" t="s">
+      <c r="A43" s="529" t="s">
         <v>78</v>
       </c>
-      <c r="B43" s="135" t="s">
+      <c r="B43" s="530" t="s">
         <v>122</v>
       </c>
-      <c r="C43" s="136">
+      <c r="C43" s="531">
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="137" t="s">
+      <c r="A44" s="532" t="s">
         <v>79</v>
       </c>
-      <c r="B44" s="138" t="s">
+      <c r="B44" s="533" t="s">
         <v>123</v>
       </c>
-      <c r="C44" s="139">
+      <c r="C44" s="534">
         <v>1.2882067767286116</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="140" t="s">
+      <c r="A45" s="535" t="s">
         <v>79</v>
       </c>
-      <c r="B45" s="141" t="s">
+      <c r="B45" s="536" t="s">
         <v>124</v>
       </c>
-      <c r="C45" s="142">
+      <c r="C45" s="537">
         <v>-1.2997992668892628</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="143" t="s">
+      <c r="A46" s="538" t="s">
         <v>79</v>
       </c>
-      <c r="B46" s="144" t="s">
+      <c r="B46" s="539" t="s">
         <v>125</v>
       </c>
-      <c r="C46" s="145">
+      <c r="C46" s="540">
         <v>3.0061833640683528</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="146" t="s">
+      <c r="A47" s="541" t="s">
         <v>79</v>
       </c>
-      <c r="B47" s="147" t="s">
+      <c r="B47" s="542" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="148">
+      <c r="C47" s="543">
         <v>-0.17645640138388471</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="149" t="s">
+      <c r="A48" s="544" t="s">
         <v>79</v>
       </c>
-      <c r="B48" s="150" t="s">
+      <c r="B48" s="545" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="151">
+      <c r="C48" s="546">
         <v>-0.33236078889173015</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="152" t="s">
+      <c r="A49" s="547" t="s">
         <v>79</v>
       </c>
-      <c r="B49" s="153" t="s">
+      <c r="B49" s="548" t="s">
         <v>34</v>
       </c>
-      <c r="C49" s="154">
+      <c r="C49" s="549">
         <v>0.1194392416837517</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="155" t="s">
+      <c r="A50" s="550" t="s">
         <v>79</v>
       </c>
-      <c r="B50" s="156" t="s">
+      <c r="B50" s="551" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="157">
+      <c r="C50" s="552">
         <v>0.068414870227888822</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="158" t="s">
+      <c r="A51" s="553" t="s">
         <v>79</v>
       </c>
-      <c r="B51" s="159" t="s">
+      <c r="B51" s="554" t="s">
         <v>36</v>
       </c>
-      <c r="C51" s="160">
+      <c r="C51" s="555">
         <v>0.17073812889865861</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="161" t="s">
+      <c r="A52" s="556" t="s">
         <v>79</v>
       </c>
-      <c r="B52" s="162" t="s">
+      <c r="B52" s="557" t="s">
         <v>37</v>
       </c>
-      <c r="C52" s="163">
+      <c r="C52" s="558">
         <v>0.31008172045906679</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="164" t="s">
+      <c r="A53" s="559" t="s">
         <v>79</v>
       </c>
-      <c r="B53" s="165" t="s">
+      <c r="B53" s="560" t="s">
         <v>38</v>
       </c>
-      <c r="C53" s="166">
+      <c r="C53" s="561">
         <v>0.30640168096709297</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="167" t="s">
+      <c r="A54" s="562" t="s">
         <v>79</v>
       </c>
-      <c r="B54" s="168" t="s">
+      <c r="B54" s="563" t="s">
         <v>39</v>
       </c>
-      <c r="C54" s="169">
+      <c r="C54" s="564">
         <v>0.16318331786500195</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="170" t="s">
+      <c r="A55" s="565" t="s">
         <v>79</v>
       </c>
-      <c r="B55" s="171" t="s">
+      <c r="B55" s="566" t="s">
         <v>40</v>
       </c>
-      <c r="C55" s="172">
+      <c r="C55" s="567">
         <v>0.52756957952222028</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="173" t="s">
+      <c r="A56" s="568" t="s">
         <v>79</v>
       </c>
-      <c r="B56" s="174" t="s">
+      <c r="B56" s="569" t="s">
         <v>41</v>
       </c>
-      <c r="C56" s="175">
+      <c r="C56" s="570">
         <v>0.39613351115466361</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="176" t="s">
+      <c r="A57" s="571" t="s">
         <v>79</v>
       </c>
-      <c r="B57" s="177" t="s">
+      <c r="B57" s="572" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="178">
+      <c r="C57" s="573">
         <v>0.52573077979661709</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="179" t="s">
+      <c r="A58" s="574" t="s">
         <v>79</v>
       </c>
-      <c r="B58" s="180" t="s">
+      <c r="B58" s="575" t="s">
         <v>43</v>
       </c>
-      <c r="C58" s="181">
+      <c r="C58" s="576">
         <v>-0.24304804126291357</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="182" t="s">
+      <c r="A59" s="577" t="s">
         <v>79</v>
       </c>
-      <c r="B59" s="183" t="s">
+      <c r="B59" s="578" t="s">
         <v>44</v>
       </c>
-      <c r="C59" s="184">
+      <c r="C59" s="579">
         <v>-0.36247072258923752</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="185" t="s">
+      <c r="A60" s="580" t="s">
         <v>79</v>
       </c>
-      <c r="B60" s="186" t="s">
+      <c r="B60" s="581" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="187">
+      <c r="C60" s="582">
         <v>-0.51265953517804408</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="188" t="s">
+      <c r="A61" s="583" t="s">
         <v>79</v>
       </c>
-      <c r="B61" s="189" t="s">
+      <c r="B61" s="584" t="s">
         <v>46</v>
       </c>
-      <c r="C61" s="190">
+      <c r="C61" s="585">
         <v>-1.3391132071495899</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="191" t="s">
+      <c r="A62" s="586" t="s">
         <v>79</v>
       </c>
-      <c r="B62" s="192" t="s">
+      <c r="B62" s="587" t="s">
         <v>47</v>
       </c>
-      <c r="C62" s="193">
+      <c r="C62" s="588">
         <v>-0.68860266148727944</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="194" t="s">
+      <c r="A63" s="589" t="s">
         <v>79</v>
       </c>
-      <c r="B63" s="195" t="s">
+      <c r="B63" s="590" t="s">
         <v>48</v>
       </c>
-      <c r="C63" s="196">
+      <c r="C63" s="591">
         <v>-0.24780224087154051</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="197" t="s">
+      <c r="A64" s="592" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="198" t="s">
+      <c r="B64" s="593" t="s">
         <v>49</v>
       </c>
-      <c r="C64" s="199">
+      <c r="C64" s="594">
         <v>-0.30128733203654995</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="200" t="s">
+      <c r="A65" s="595" t="s">
         <v>79</v>
       </c>
-      <c r="B65" s="201" t="s">
+      <c r="B65" s="596" t="s">
         <v>73</v>
       </c>
-      <c r="C65" s="202">
+      <c r="C65" s="597">
         <v>0.26060720823703976</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="203" t="s">
+      <c r="A66" s="598" t="s">
         <v>79</v>
       </c>
-      <c r="B66" s="204" t="s">
+      <c r="B66" s="599" t="s">
         <v>74</v>
       </c>
-      <c r="C66" s="205">
+      <c r="C66" s="600">
         <v>0.29704631812288285</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="206" t="s">
+      <c r="A67" s="601" t="s">
         <v>79</v>
       </c>
-      <c r="B67" s="207" t="s">
+      <c r="B67" s="602" t="s">
         <v>75</v>
       </c>
-      <c r="C67" s="208">
+      <c r="C67" s="603">
         <v>0.62392706597049674</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="209" t="s">
+      <c r="A68" s="604" t="s">
         <v>79</v>
       </c>
-      <c r="B68" s="210" t="s">
+      <c r="B68" s="605" t="s">
         <v>76</v>
       </c>
-      <c r="C68" s="211">
+      <c r="C68" s="606">
         <v>0.20022039439675773</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="212" t="s">
+      <c r="A69" s="607" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="213" t="s">
+      <c r="B69" s="608" t="s">
         <v>50</v>
       </c>
-      <c r="C69" s="214">
+      <c r="C69" s="609">
         <v>-0.2004621778396502</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="215" t="s">
+      <c r="A70" s="610" t="s">
         <v>79</v>
       </c>
-      <c r="B70" s="216" t="s">
+      <c r="B70" s="611" t="s">
         <v>51</v>
       </c>
-      <c r="C70" s="217">
+      <c r="C70" s="612">
         <v>-0.1462818915071871</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="218" t="s">
+      <c r="A71" s="613" t="s">
         <v>79</v>
       </c>
-      <c r="B71" s="219" t="s">
+      <c r="B71" s="614" t="s">
         <v>52</v>
       </c>
-      <c r="C71" s="220">
+      <c r="C71" s="615">
         <v>-0.093365838157548564</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="221" t="s">
+      <c r="A72" s="616" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="222" t="s">
+      <c r="B72" s="617" t="s">
         <v>53</v>
       </c>
-      <c r="C72" s="223">
+      <c r="C72" s="618">
         <v>0.050141178173999615</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="224" t="s">
+      <c r="A73" s="619" t="s">
         <v>79</v>
       </c>
-      <c r="B73" s="225" t="s">
+      <c r="B73" s="620" t="s">
         <v>54</v>
       </c>
-      <c r="C73" s="226">
+      <c r="C73" s="621">
         <v>0.23601777677506255</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="227" t="s">
+      <c r="A74" s="622" t="s">
         <v>79</v>
       </c>
-      <c r="B74" s="228" t="s">
+      <c r="B74" s="623" t="s">
         <v>55</v>
       </c>
-      <c r="C74" s="229">
+      <c r="C74" s="624">
         <v>-0.1136795775817719</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="230" t="s">
+      <c r="A75" s="625" t="s">
         <v>79</v>
       </c>
-      <c r="B75" s="231" t="s">
+      <c r="B75" s="626" t="s">
         <v>56</v>
       </c>
-      <c r="C75" s="232">
+      <c r="C75" s="627">
         <v>-0.052040824344087383</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="233" t="s">
+      <c r="A76" s="628" t="s">
         <v>79</v>
       </c>
-      <c r="B76" s="234" t="s">
+      <c r="B76" s="629" t="s">
         <v>57</v>
       </c>
-      <c r="C76" s="235">
+      <c r="C76" s="630">
         <v>0.46944934794520449</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="236" t="s">
+      <c r="A77" s="631" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="237" t="s">
+      <c r="B77" s="632" t="s">
         <v>58</v>
       </c>
-      <c r="C77" s="238">
+      <c r="C77" s="633">
         <v>0.23318380786682447</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="239" t="s">
+      <c r="A78" s="634" t="s">
         <v>79</v>
       </c>
-      <c r="B78" s="240" t="s">
+      <c r="B78" s="635" t="s">
         <v>59</v>
       </c>
-      <c r="C78" s="241">
+      <c r="C78" s="636">
         <v>0.24057498437679456</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="242" t="s">
+      <c r="A79" s="637" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="243" t="s">
+      <c r="B79" s="638" t="s">
         <v>60</v>
       </c>
-      <c r="C79" s="244">
+      <c r="C79" s="639">
         <v>0.0047103274644143892</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="245" t="s">
+      <c r="A80" s="640" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="246" t="s">
+      <c r="B80" s="641" t="s">
         <v>61</v>
       </c>
-      <c r="C80" s="247">
+      <c r="C80" s="642">
         <v>0.26503680694452686</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="248" t="s">
+      <c r="A81" s="643" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="249" t="s">
+      <c r="B81" s="644" t="s">
         <v>62</v>
       </c>
-      <c r="C81" s="250">
+      <c r="C81" s="645">
         <v>0.32710704617526015</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="251" t="s">
+      <c r="A82" s="646" t="s">
         <v>79</v>
       </c>
-      <c r="B82" s="252" t="s">
+      <c r="B82" s="647" t="s">
         <v>63</v>
       </c>
-      <c r="C82" s="253">
+      <c r="C82" s="648">
         <v>-0.061780931661149681</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="254" t="s">
+      <c r="A83" s="649" t="s">
         <v>79</v>
       </c>
-      <c r="B83" s="255" t="s">
+      <c r="B83" s="650" t="s">
         <v>64</v>
       </c>
-      <c r="C83" s="256">
+      <c r="C83" s="651">
         <v>-0.14216213083859588</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="257" t="s">
+      <c r="A84" s="652" t="s">
         <v>79</v>
       </c>
-      <c r="B84" s="258" t="s">
+      <c r="B84" s="653" t="s">
         <v>65</v>
       </c>
-      <c r="C84" s="259">
+      <c r="C84" s="654">
         <v>0.39424155363966507</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="260" t="s">
+      <c r="A85" s="655" t="s">
         <v>79</v>
       </c>
-      <c r="B85" s="261" t="s">
+      <c r="B85" s="656" t="s">
         <v>126</v>
       </c>
-      <c r="C85" s="262">
+      <c r="C85" s="657">
         <v>-1.0939468397898455</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="263" t="s">
+      <c r="A86" s="658" t="s">
         <v>80</v>
       </c>
-      <c r="B86" s="264" t="s">
+      <c r="B86" s="659" t="s">
         <v>123</v>
       </c>
-      <c r="C86" s="265">
+      <c r="C86" s="660">
         <v>3.7931302309684729</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="266" t="s">
+      <c r="A87" s="661" t="s">
         <v>80</v>
       </c>
-      <c r="B87" s="267" t="s">
+      <c r="B87" s="662" t="s">
         <v>124</v>
       </c>
-      <c r="C87" s="268">
+      <c r="C87" s="663">
         <v>-2.6684359456994255</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="269" t="s">
+      <c r="A88" s="664" t="s">
         <v>80</v>
       </c>
-      <c r="B88" s="270" t="s">
+      <c r="B88" s="665" t="s">
         <v>125</v>
       </c>
-      <c r="C88" s="271">
+      <c r="C88" s="666">
         <v>0.65075334723696276</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="272" t="s">
+      <c r="A89" s="667" t="s">
         <v>80</v>
       </c>
-      <c r="B89" s="273" t="s">
+      <c r="B89" s="668" t="s">
         <v>32</v>
       </c>
-      <c r="C89" s="274">
+      <c r="C89" s="669">
         <v>-0.078099983499234374</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="275" t="s">
+      <c r="A90" s="670" t="s">
         <v>80</v>
       </c>
-      <c r="B90" s="276" t="s">
+      <c r="B90" s="671" t="s">
         <v>33</v>
       </c>
-      <c r="C90" s="277">
+      <c r="C90" s="672">
         <v>0.24288808734557116</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="278" t="s">
+      <c r="A91" s="673" t="s">
         <v>80</v>
       </c>
-      <c r="B91" s="279" t="s">
+      <c r="B91" s="674" t="s">
         <v>34</v>
       </c>
-      <c r="C91" s="280">
+      <c r="C91" s="675">
         <v>0.23240872935037771</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="281" t="s">
+      <c r="A92" s="676" t="s">
         <v>80</v>
       </c>
-      <c r="B92" s="282" t="s">
+      <c r="B92" s="677" t="s">
         <v>35</v>
       </c>
-      <c r="C92" s="283">
+      <c r="C92" s="678">
         <v>0.19407809657995287</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="284" t="s">
+      <c r="A93" s="679" t="s">
         <v>80</v>
       </c>
-      <c r="B93" s="285" t="s">
+      <c r="B93" s="680" t="s">
         <v>36</v>
       </c>
-      <c r="C93" s="286">
+      <c r="C93" s="681">
         <v>0.75345404471688937</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="287" t="s">
+      <c r="A94" s="682" t="s">
         <v>80</v>
       </c>
-      <c r="B94" s="288" t="s">
+      <c r="B94" s="683" t="s">
         <v>37</v>
       </c>
-      <c r="C94" s="289">
+      <c r="C94" s="684">
         <v>0.35950513610799095</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="290" t="s">
+      <c r="A95" s="685" t="s">
         <v>80</v>
       </c>
-      <c r="B95" s="291" t="s">
+      <c r="B95" s="686" t="s">
         <v>38</v>
       </c>
-      <c r="C95" s="292">
+      <c r="C95" s="687">
         <v>-0.082680047810493512</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="293" t="s">
+      <c r="A96" s="688" t="s">
         <v>80</v>
       </c>
-      <c r="B96" s="294" t="s">
+      <c r="B96" s="689" t="s">
         <v>39</v>
       </c>
-      <c r="C96" s="295">
+      <c r="C96" s="690">
         <v>0.56905439628838428</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="296" t="s">
+      <c r="A97" s="691" t="s">
         <v>80</v>
       </c>
-      <c r="B97" s="297" t="s">
+      <c r="B97" s="692" t="s">
         <v>40</v>
       </c>
-      <c r="C97" s="298">
+      <c r="C97" s="693">
         <v>0.48041986891890481</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="299" t="s">
+      <c r="A98" s="694" t="s">
         <v>80</v>
       </c>
-      <c r="B98" s="300" t="s">
+      <c r="B98" s="695" t="s">
         <v>41</v>
       </c>
-      <c r="C98" s="301">
+      <c r="C98" s="696">
         <v>0.37518674471812674</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="302" t="s">
+      <c r="A99" s="697" t="s">
         <v>80</v>
       </c>
-      <c r="B99" s="303" t="s">
+      <c r="B99" s="698" t="s">
         <v>42</v>
       </c>
-      <c r="C99" s="304">
+      <c r="C99" s="699">
         <v>0.30335325341065222</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="305" t="s">
+      <c r="A100" s="700" t="s">
         <v>80</v>
       </c>
-      <c r="B100" s="306" t="s">
+      <c r="B100" s="701" t="s">
         <v>43</v>
       </c>
-      <c r="C100" s="307">
+      <c r="C100" s="702">
         <v>0.020787210405927202</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="308" t="s">
+      <c r="A101" s="703" t="s">
         <v>80</v>
       </c>
-      <c r="B101" s="309" t="s">
+      <c r="B101" s="704" t="s">
         <v>44</v>
       </c>
-      <c r="C101" s="310">
+      <c r="C101" s="705">
         <v>0.26254367397572631</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="311" t="s">
+      <c r="A102" s="706" t="s">
         <v>80</v>
       </c>
-      <c r="B102" s="312" t="s">
+      <c r="B102" s="707" t="s">
         <v>45</v>
       </c>
-      <c r="C102" s="313">
+      <c r="C102" s="708">
         <v>0.51396373609336943</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="314" t="s">
+      <c r="A103" s="709" t="s">
         <v>80</v>
       </c>
-      <c r="B103" s="315" t="s">
+      <c r="B103" s="710" t="s">
         <v>46</v>
       </c>
-      <c r="C103" s="316">
+      <c r="C103" s="711">
         <v>-0.13245418010244187</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="317" t="s">
+      <c r="A104" s="712" t="s">
         <v>80</v>
       </c>
-      <c r="B104" s="318" t="s">
+      <c r="B104" s="713" t="s">
         <v>47</v>
       </c>
-      <c r="C104" s="319">
+      <c r="C104" s="714">
         <v>-1.9571774514089817</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="320" t="s">
+      <c r="A105" s="715" t="s">
         <v>80</v>
       </c>
-      <c r="B105" s="321" t="s">
+      <c r="B105" s="716" t="s">
         <v>48</v>
       </c>
-      <c r="C105" s="322">
+      <c r="C105" s="717">
         <v>-0.44065949013840416</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="323" t="s">
+      <c r="A106" s="718" t="s">
         <v>80</v>
       </c>
-      <c r="B106" s="324" t="s">
+      <c r="B106" s="719" t="s">
         <v>49</v>
       </c>
-      <c r="C106" s="325">
+      <c r="C106" s="720">
         <v>-0.95797349111650854</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="326" t="s">
+      <c r="A107" s="721" t="s">
         <v>80</v>
       </c>
-      <c r="B107" s="327" t="s">
+      <c r="B107" s="722" t="s">
         <v>73</v>
       </c>
-      <c r="C107" s="328">
+      <c r="C107" s="723">
         <v>0.0042543417517892082</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="329" t="s">
+      <c r="A108" s="724" t="s">
         <v>80</v>
       </c>
-      <c r="B108" s="330" t="s">
+      <c r="B108" s="725" t="s">
         <v>74</v>
       </c>
-      <c r="C108" s="331">
+      <c r="C108" s="726">
         <v>0.58668651287970652</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="332" t="s">
+      <c r="A109" s="727" t="s">
         <v>80</v>
       </c>
-      <c r="B109" s="333" t="s">
+      <c r="B109" s="728" t="s">
         <v>75</v>
       </c>
-      <c r="C109" s="334">
+      <c r="C109" s="729">
         <v>0.59997188961404779</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="335" t="s">
+      <c r="A110" s="730" t="s">
         <v>80</v>
       </c>
-      <c r="B110" s="336" t="s">
+      <c r="B110" s="731" t="s">
         <v>76</v>
       </c>
-      <c r="C110" s="337">
+      <c r="C110" s="732">
         <v>1.0040886251429342</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="338" t="s">
+      <c r="A111" s="733" t="s">
         <v>80</v>
       </c>
-      <c r="B111" s="339" t="s">
+      <c r="B111" s="734" t="s">
         <v>50</v>
       </c>
-      <c r="C111" s="340">
+      <c r="C111" s="735">
         <v>-0.37603417561200547</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="341" t="s">
+      <c r="A112" s="736" t="s">
         <v>80</v>
       </c>
-      <c r="B112" s="342" t="s">
+      <c r="B112" s="737" t="s">
         <v>51</v>
       </c>
-      <c r="C112" s="343">
+      <c r="C112" s="738">
         <v>-0.89407955053464394</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="344" t="s">
+      <c r="A113" s="739" t="s">
         <v>80</v>
       </c>
-      <c r="B113" s="345" t="s">
+      <c r="B113" s="740" t="s">
         <v>52</v>
       </c>
-      <c r="C113" s="346">
+      <c r="C113" s="741">
         <v>-0.64903957293475478</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="347" t="s">
+      <c r="A114" s="742" t="s">
         <v>80</v>
       </c>
-      <c r="B114" s="348" t="s">
+      <c r="B114" s="743" t="s">
         <v>53</v>
       </c>
-      <c r="C114" s="349">
+      <c r="C114" s="744">
         <v>0.032713186737036479</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="350" t="s">
+      <c r="A115" s="745" t="s">
         <v>80</v>
       </c>
-      <c r="B115" s="351" t="s">
+      <c r="B115" s="746" t="s">
         <v>54</v>
       </c>
-      <c r="C115" s="352">
+      <c r="C115" s="747">
         <v>0.064308765592442821</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="353" t="s">
+      <c r="A116" s="748" t="s">
         <v>80</v>
       </c>
-      <c r="B116" s="354" t="s">
+      <c r="B116" s="749" t="s">
         <v>55</v>
       </c>
-      <c r="C116" s="355">
+      <c r="C116" s="750">
         <v>-0.23035678631441375</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="356" t="s">
+      <c r="A117" s="751" t="s">
         <v>80</v>
       </c>
-      <c r="B117" s="357" t="s">
+      <c r="B117" s="752" t="s">
         <v>56</v>
       </c>
-      <c r="C117" s="358">
+      <c r="C117" s="753">
         <v>-0.15346894107656445</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="359" t="s">
+      <c r="A118" s="754" t="s">
         <v>80</v>
       </c>
-      <c r="B118" s="360" t="s">
+      <c r="B118" s="755" t="s">
         <v>57</v>
       </c>
-      <c r="C118" s="361">
+      <c r="C118" s="756">
         <v>0.18721141881743772</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="362" t="s">
+      <c r="A119" s="757" t="s">
         <v>80</v>
       </c>
-      <c r="B119" s="363" t="s">
+      <c r="B119" s="758" t="s">
         <v>58</v>
       </c>
-      <c r="C119" s="364">
+      <c r="C119" s="759">
         <v>0.035828058091675233</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="365" t="s">
+      <c r="A120" s="760" t="s">
         <v>80</v>
       </c>
-      <c r="B120" s="366" t="s">
+      <c r="B120" s="761" t="s">
         <v>59</v>
       </c>
-      <c r="C120" s="367">
+      <c r="C120" s="762">
         <v>0.33163280693237523</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="368" t="s">
+      <c r="A121" s="763" t="s">
         <v>80</v>
       </c>
-      <c r="B121" s="369" t="s">
+      <c r="B121" s="764" t="s">
         <v>60</v>
       </c>
-      <c r="C121" s="370">
+      <c r="C121" s="765">
         <v>0.015584048330157831</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="371" t="s">
+      <c r="A122" s="766" t="s">
         <v>80</v>
       </c>
-      <c r="B122" s="372" t="s">
+      <c r="B122" s="767" t="s">
         <v>61</v>
       </c>
-      <c r="C122" s="373">
+      <c r="C122" s="768">
         <v>-0.17025911130351387</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="374" t="s">
+      <c r="A123" s="769" t="s">
         <v>80</v>
       </c>
-      <c r="B123" s="375" t="s">
+      <c r="B123" s="770" t="s">
         <v>62</v>
       </c>
-      <c r="C123" s="376">
+      <c r="C123" s="771">
         <v>0.28777399094357636</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="377" t="s">
+      <c r="A124" s="772" t="s">
         <v>80</v>
       </c>
-      <c r="B124" s="378" t="s">
+      <c r="B124" s="773" t="s">
         <v>63</v>
       </c>
-      <c r="C124" s="379">
+      <c r="C124" s="774">
         <v>-0.31364266806692587</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="380" t="s">
+      <c r="A125" s="775" t="s">
         <v>80</v>
       </c>
-      <c r="B125" s="381" t="s">
+      <c r="B125" s="776" t="s">
         <v>64</v>
       </c>
-      <c r="C125" s="382">
+      <c r="C125" s="777">
         <v>-0.6222289472997099</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="383" t="s">
+      <c r="A126" s="778" t="s">
         <v>80</v>
       </c>
-      <c r="B126" s="384" t="s">
+      <c r="B126" s="779" t="s">
         <v>65</v>
       </c>
-      <c r="C126" s="385">
+      <c r="C126" s="780">
         <v>0.30525873658672231</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="386" t="s">
+      <c r="A127" s="781" t="s">
         <v>80</v>
       </c>
-      <c r="B127" s="387" t="s">
+      <c r="B127" s="782" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="388">
+      <c r="C127" s="783">
         <v>-0.96075645581973834</v>
       </c>
     </row>
